--- a/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/d1_m2_formatting_answers.xlsx
+++ b/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/d1_m2_formatting_answers.xlsx
@@ -576,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -648,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -684,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -720,7 +720,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -756,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1008,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/d1_m2_formatting_answers.xlsx
+++ b/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/d1_m2_formatting_answers.xlsx
@@ -457,8 +457,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="19.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -672,19 +672,19 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7">
@@ -694,33 +694,33 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Chinhoyi</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home Device</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -730,33 +730,33 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Bulawayo</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Smart Home Device</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -802,33 +802,33 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kwekwe</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -838,33 +838,33 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Chitungwiza</t>
+          <t>Gweru</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
@@ -874,33 +874,33 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mutare</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -910,33 +910,33 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home Device</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kwekwe</t>
+          <t>Masvingo</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15">
@@ -982,33 +982,33 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Chitungwiza</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Smart Home Device</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -1018,33 +1018,33 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
